--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46230</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45847</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44950</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46034</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45855</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45321</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45264</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45551</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46251</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45502</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>45366</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45986</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>46003</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44748</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45072</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45603</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45337</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>44474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45335</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45202</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45082</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46003</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46006</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>46055</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>46077</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45645</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45357</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>45576</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45355</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44512</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44469</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44529</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44503</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44560</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44559</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44470</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44602</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44490</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44823</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44739</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44503</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44529</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44594</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44497</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44530</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44802</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>44545</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>44636</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44636</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44578</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44729</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44503</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44711</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44728</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44475</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44707</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44529</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>44623</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>44622</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>44580</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>44474</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44824</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>45757</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45616</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45091</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45251</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44802</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>45110</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45443</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>45755</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>45105</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45700</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45123</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45162</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45687</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>45187</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45324</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45204</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45085</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>45363</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>45199</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>45550</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>44861</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>44573</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>45334</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45226</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44594</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>44747</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>45551</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>45033</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>45111</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44629</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>45649</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>45540</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45540</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>45485</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>45454</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>45146</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44980</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>45033</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44672</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45330</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45217</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45237</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45036</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45062</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45073</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>45049</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>45307</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45551</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>45342</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>45586</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44838</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45891</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>45148</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45749</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         <v>44630</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45250</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>45343</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12105,7 +12105,7 @@
         <v>45775</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>45645</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45462</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45350</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44832</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45798</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>45370</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>45642</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45908</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45595</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45909</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44979</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45180</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>44489</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13132,7 +13132,7 @@
         <v>44838</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45274</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>45925</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>44805</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>45925</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>45925</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>44922</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44461</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45929</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45675</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>44952</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45775</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>45934</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45934</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>45940</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45623</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44882</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45257</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45947</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45161</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44489</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45958</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45959</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>45259</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45964</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45685</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45764</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45694</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45616</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45616</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>44811</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45092</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>44497</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45978</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44928</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>44928</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>44630</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>44630</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45699</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45033</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44627</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45974</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45622</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45645</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45988</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45014</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45988</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>44645</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45896</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45226</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44823</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44823</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>44956</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45219</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45994</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>46163</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45629</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45103</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>44985</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>44704</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>45154</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>44957</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>45161</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>46003</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45606</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45384</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>46006</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>46006</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45187</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45225</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>46010</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45226</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45084</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45050</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45133</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>46170</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45194</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>46029</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>46029</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45609</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45169</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>45203</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45511</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>46038</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45148</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45244</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>46042</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>46042</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>46043</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45870</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>46045</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>46176</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45050</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>46055</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>46055</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>44812</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>46057</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45236</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45022</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>46063</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45728</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>46069</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>46069</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>46071</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45197</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>46072</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>46074</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44713</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>45705</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>45679</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44952</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45414</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>45111</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45107</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>46090</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45112</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45093</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45511</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45384</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>46090</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>46094</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>46093</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45085</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22637,7 +22637,7 @@
         <v>45511</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>44812</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>46101</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22856,7 +22856,7 @@
         <v>46197</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45511</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>45553</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>46202</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23148,7 +23148,7 @@
         <v>44690</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>46114</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>46119</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23372,7 +23372,7 @@
         <v>45384</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>46126</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>45352</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>46132</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>46132</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>46133</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>46133</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>45539</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>46135</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>45210</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>46139</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45271</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45642</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45642</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45028</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45688</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>44722</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>45700</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45700</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45217</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>46248</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>45558</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45593</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>44747</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45188</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>46252</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45559</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45343</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>46252</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>46210</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>46252</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>46252</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>46252</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45796</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45462</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45462</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>46210</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>44592</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>46211</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>46043</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46210</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>45204</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>46211</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46254</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>46038</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44987</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45076</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>46221</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>46221</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45426</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27027,7 +27027,7 @@
         <v>45040</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45040</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45485</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45168</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>46221</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45622</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>46164</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>46264</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>46269</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>45646</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>46269</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>46269</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45777</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45777</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45777</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45777</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>46274</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>46274</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>46274</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>46276</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45728</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45709</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45757</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45426</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45525</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45278</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45233</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45618</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45090</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45740</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45740</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45797</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45637</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45366</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45805</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45511</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45808</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45808</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45473</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44974</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45816</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45741</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>44623</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45727</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44529</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>44949</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45833</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45303</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45600</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>44952</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>45601</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>45593</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>45727</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>45726</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>45867</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>45870</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45400</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44980</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>44865</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>44981</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45355</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>44981</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45716</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45939</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>46147</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>

--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>46230</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>46034</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>45831</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>45855</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45321</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>46251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45264</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45603</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45502</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45559</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44748</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45986</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>46003</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45091</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45366</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45072</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>44474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45202</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>46055</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>45357</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>46077</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>45082</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45645</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>46006</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>46003</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45576</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>45335</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45355</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44469</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44529</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44503</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44470</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44560</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44559</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44490</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44823</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44739</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44503</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44497</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44802</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>44636</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>44636</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44578</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44729</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44503</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44711</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44728</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44475</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44707</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>44622</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>44474</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>44580</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>44824</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>45219</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44823</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44823</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45203</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45187</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45343</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45050</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>45705</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45363</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>44928</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45226</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45443</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44952</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>45226</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45426</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45257</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>44489</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>45462</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>45133</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>46029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>45511</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45384</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>45485</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>46029</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>44630</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>44985</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>45622</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>46038</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>46042</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>46042</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45050</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>46043</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45148</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>46045</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45908</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>46055</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>45909</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>46055</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45551</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>46057</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45343</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45606</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45366</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45728</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>44952</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>46063</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45350</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>44489</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45559</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>46069</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>46069</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45014</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>46071</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45925</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46072</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44838</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44838</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45370</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>46074</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>45925</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45925</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45930</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45511</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45805</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45550</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>44629</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45511</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45473</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45808</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45808</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>44630</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44630</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45934</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45934</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>46090</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45936</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>46090</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>46093</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45940</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46094</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>44974</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45630</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>46101</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>44645</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45947</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45553</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45085</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45958</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>44713</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45694</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>46114</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45959</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45609</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>46119</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45964</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>46126</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44497</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45414</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45454</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45816</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45741</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>46132</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>46132</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45978</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45616</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45342</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45645</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45988</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45988</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45616</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>46135</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45775</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>44623</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45994</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45642</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45994</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45727</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45798</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>46006</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>46003</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>46006</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45687</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>46010</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45210</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45622</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45236</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45749</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>46139</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45511</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45700</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45700</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45111</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44949</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45091</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45485</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44529</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44922</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45028</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45303</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45330</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45833</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44956</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>44903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45105</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45092</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45107</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45217</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45217</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45764</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45896</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45699</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45645</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45974</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>46163</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45600</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45595</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45601</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44952</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44957</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45593</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45352</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45727</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45324</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45726</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45870</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>46170</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45112</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45384</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44980</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45867</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>46176</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45870</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45551</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44987</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45076</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45148</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45539</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45022</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45586</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45642</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45642</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45073</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45334</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45168</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46197</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45511</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45757</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45180</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45649</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45623</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45084</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>46202</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44802</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>46252</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>46252</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>46252</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45194</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>46252</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44573</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45103</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>46252</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45679</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>46210</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>46043</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>46210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>46211</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>46210</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45629</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>46211</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45148</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>46038</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>46254</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45154</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45685</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45085</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45700</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45199</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45237</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45251</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>45688</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>44672</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45197</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45307</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45244</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>46221</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>45250</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>46221</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>46221</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>46264</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44704</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44805</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>46164</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>46269</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>46269</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>46269</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45271</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44812</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>46274</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>46274</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>46276</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45259</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44627</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45162</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>46286</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44861</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45040</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45033</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>46287</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45384</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45033</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46288</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>46288</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>44979</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46288</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45161</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44812</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>44592</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45204</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>46248</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45558</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>44594</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>44882</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45274</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>44722</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45040</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45755</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45146</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45033</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44838</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44832</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45111</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45036</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44747</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>44747</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45462</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45462</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45188</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45675</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45169</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45110</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45062</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45187</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45540</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45204</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>44811</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45123</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45646</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>44690</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45097</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45488</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45616</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45093</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45775</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45049</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>45225</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45777</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45777</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45777</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45777</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45426</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45728</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45090</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45757</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45740</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45740</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45233</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45278</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45709</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45618</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45525</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45400</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44980</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44865</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44981</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45355</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44981</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45716</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45939</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>46147</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>

--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>46230</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>46034</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>45831</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>45855</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>44950</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45321</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>46251</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45264</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45603</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45502</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45559</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>44748</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45986</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45337</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>46003</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45091</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45366</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45072</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>44474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45202</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>46055</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>45357</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>46077</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>45082</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45645</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>46006</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>46003</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>45576</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>45335</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45355</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44469</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44529</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44503</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44470</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44560</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44559</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44490</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44823</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44739</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44503</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44529</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44594</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44497</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44802</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44545</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>44636</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>44636</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44578</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44729</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>44503</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44711</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44728</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44475</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44707</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44529</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44529</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44623</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>44622</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>44474</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>44580</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>44824</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>45219</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44823</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>44823</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45203</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45187</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45343</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45050</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>45705</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45363</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>44928</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45226</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45443</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44952</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45226</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>45226</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45426</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45257</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>44489</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>45462</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>45133</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>46029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>45511</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45384</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>45485</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>46029</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>44630</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>44985</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>45622</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>46038</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>46042</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>46042</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>45050</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>46043</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>45148</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>46045</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45908</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>46055</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>45909</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>46055</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45551</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>46057</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45343</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45606</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45366</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45728</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>44952</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>46063</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45350</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>44489</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>45559</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>46069</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>46069</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45014</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>46071</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45925</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46072</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44838</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>44838</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45370</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>46074</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>45925</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45925</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45930</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45511</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45805</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45550</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>44629</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>45511</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45473</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45808</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45808</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>44630</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44630</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45934</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45934</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>46090</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45936</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>46090</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>46093</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45940</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46094</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>44974</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45630</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>46101</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>44645</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45947</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45553</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>45085</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45958</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>44713</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45694</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>46114</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45959</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45609</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>46119</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45964</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>46126</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>44497</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>45414</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45454</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45816</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45741</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>46132</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>46132</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45978</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45616</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45593</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45342</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45645</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45988</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45988</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45616</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>46135</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45775</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>44623</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45994</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45642</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45994</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45727</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45798</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>46006</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>46003</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>46006</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>45687</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>46010</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>45210</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>45622</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45236</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45749</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>46139</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45511</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45700</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45700</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45111</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44949</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45091</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45485</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44529</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>44922</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45028</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45303</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>45330</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>45833</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>44956</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>44903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>45105</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45092</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45107</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45217</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45217</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45764</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45896</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45699</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45645</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45974</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>46163</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45600</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>45595</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45601</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44952</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44957</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45593</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45352</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45727</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45324</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45726</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>45870</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>46170</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45112</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45384</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44980</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45867</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>46176</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45870</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>45551</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44987</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45076</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>45148</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45539</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45022</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45586</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45642</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45642</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45073</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45334</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45168</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>46197</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>45511</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45757</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>45180</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45649</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45623</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45084</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         <v>46202</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44802</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>46252</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>46252</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>46252</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
         <v>45194</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>46252</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44573</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45103</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>46252</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>45679</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23065,7 +23065,7 @@
         <v>46210</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>46043</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>46210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>46211</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>46210</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45629</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>46211</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45148</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>46038</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23722,7 +23722,7 @@
         <v>46254</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45154</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45685</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45085</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45700</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45199</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45237</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45251</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>45688</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>44672</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45197</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45307</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45244</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24671,7 +24671,7 @@
         <v>46221</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>45250</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>46221</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>46221</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>46264</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>44704</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44805</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>46164</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>46269</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>46269</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>46269</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45271</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>44812</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>46274</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>46274</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>46276</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>45259</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44627</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45162</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>46286</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44861</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45040</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>45033</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>46287</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>45384</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45033</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>46288</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>46288</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>44979</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46288</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>45161</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44812</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>44592</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45204</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>46248</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45558</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>44594</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>44882</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45274</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>44722</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45040</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45755</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45146</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45033</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44838</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44832</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>45111</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45036</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>44747</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>44747</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45462</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45462</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45188</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>45675</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>45169</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45110</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45062</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>45187</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45540</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45204</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>44811</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45123</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45646</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>44690</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45097</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45488</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45616</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45093</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45775</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45049</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>45225</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45777</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45777</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45777</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45777</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45426</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45728</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45090</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45757</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45740</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45740</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>45233</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45278</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45709</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45618</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45525</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45400</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44980</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>44865</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>44981</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45355</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>44981</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45716</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45939</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>46147</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>

--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>46230</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>46034</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>45831</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>44950</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45855</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45321</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45264</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45551</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46251</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>46003</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45502</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>45337</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45986</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45366</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45091</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45072</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45232</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>44474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>46003</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46006</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>45335</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45357</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>46055</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>46077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45635</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45202</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>45082</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45576</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45645</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45355</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44529</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44503</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44559</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44602</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44490</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44823</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44739</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44503</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44529</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44594</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44497</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44530</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44802</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44545</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44636</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44636</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>44578</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>44729</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44711</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44475</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44707</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44529</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44529</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44623</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44580</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>44474</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>45757</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44802</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>45616</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45091</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45148</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45110</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45443</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45105</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>45700</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45123</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>45187</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>45324</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45755</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45162</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45687</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45204</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>45728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>46003</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45709</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45757</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>46006</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>45426</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>45525</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45085</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>46010</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>45363</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>45278</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>45233</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>45133</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>46029</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>45618</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45090</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>45550</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>46029</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45334</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>45226</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45740</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45199</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44861</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44573</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45740</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>46038</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>45908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44594</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45909</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44747</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>46042</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>46042</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>46043</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45797</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>46045</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45637</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45111</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>44629</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45551</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45033</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45366</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45805</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45511</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46055</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>46055</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45649</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45925</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45925</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>45925</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>46057</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45540</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45540</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45485</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45930</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>46063</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45728</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45146</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>45454</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45936</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>46069</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45934</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>45934</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>46069</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>46071</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>44980</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>46072</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44672</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>45033</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45940</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>46074</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45330</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45808</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45808</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45473</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45947</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45217</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>44974</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45237</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45958</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45959</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>46090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45816</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45036</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45964</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>45062</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>46094</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>46093</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45073</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45741</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>45049</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45551</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45342</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>46101</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>44623</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45978</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>45307</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45727</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45586</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44838</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>44838</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>46114</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45988</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>46119</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45988</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45994</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45488</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>46126</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45994</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45148</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>46132</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>46132</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44529</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44949</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45250</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45303</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46135</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45343</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>46139</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45462</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45350</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>44832</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45370</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45600</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45891</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45595</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44952</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45601</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44979</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45180</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45749</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45593</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44489</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44838</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45274</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45775</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45645</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45798</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45727</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>44805</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>44922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45726</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45675</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45642</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44952</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45775</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45867</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45623</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44882</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45097</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45257</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45161</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45870</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44903</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44489</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45259</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45764</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45092</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45685</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45694</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45699</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45974</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45645</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45896</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45616</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45616</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>44811</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44497</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>46163</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>44928</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>44928</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>44630</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44630</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>46170</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45033</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44627</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45622</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45014</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45870</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44645</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>46176</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>44630</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45226</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44823</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44823</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44956</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45219</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45629</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45103</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>44985</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44704</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45154</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45630</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>44957</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45161</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45606</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45384</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45187</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45225</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45226</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45084</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>46197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45050</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>46202</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45194</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45609</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45169</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45203</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45511</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>46210</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45148</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45244</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>46210</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>46211</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>46043</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>46210</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>46211</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>46038</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45050</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>44812</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>46221</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>46221</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45236</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>46221</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45022</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46164</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>46264</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45197</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46269</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46269</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46269</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44713</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45705</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45679</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>44952</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>46274</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45414</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45111</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>46274</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>46274</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>46276</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45107</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45112</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45511</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45384</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45085</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45511</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44812</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>46287</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45511</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45553</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>46286</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>46288</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44690</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45384</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>46288</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>46248</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45352</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45539</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>46294</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>46252</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45210</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>45271</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45642</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45642</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45028</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>46252</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>46252</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46252</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>46252</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45688</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>44722</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45700</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45700</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>46296</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>46296</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45217</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>46296</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>46296</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>45558</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45593</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44747</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45188</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>46296</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>46296</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>46296</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>46254</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45559</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>45343</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45462</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45462</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>44592</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45204</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44987</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45076</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45426</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>45040</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45040</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>45485</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45168</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45622</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45646</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45777</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45777</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45777</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45777</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45400</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>44980</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>44865</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44981</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45355</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44981</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45716</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45939</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>46147</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>

--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>46230</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>46034</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>45831</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>44950</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45855</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45321</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45264</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45551</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46251</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>46003</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45502</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>45337</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45986</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45366</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45091</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45072</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45232</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>44474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>46003</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46006</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>45335</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45357</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>46055</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>46077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45635</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>45202</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>45082</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45576</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45645</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>45355</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44529</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44503</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44559</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44602</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44490</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44823</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44739</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44503</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44529</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44594</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44497</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44530</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44802</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44545</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44636</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44636</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>44578</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>44729</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44711</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>44503</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44475</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44707</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44529</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44529</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44623</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44580</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>44474</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>45251</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         <v>45757</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>44802</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>45616</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>45091</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45148</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45110</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>45443</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45105</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>45700</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45123</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>45187</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>45324</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45755</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45162</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45687</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45204</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>45728</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>46003</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>45709</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         <v>45757</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>46006</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>46006</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>45426</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>45525</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45085</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>46010</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>45363</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>45278</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>45233</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>45133</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>46029</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         <v>45618</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45090</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>45550</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>46029</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45334</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>45226</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>45740</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>45199</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>44861</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44573</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45740</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>46038</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>45908</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44594</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45909</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44747</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>46042</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>46042</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>46043</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>45797</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         <v>46045</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>45637</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45111</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>44629</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45551</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>45033</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45366</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>45805</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>45511</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46055</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>46055</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45649</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45925</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45925</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>45925</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>46057</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45540</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45540</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45485</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>45930</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>46063</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         <v>45728</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45146</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>45454</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>45936</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>46069</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45934</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>45934</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>46069</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>46071</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>44980</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>46072</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44672</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>45033</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45940</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>46074</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45330</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45808</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>45808</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45473</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45947</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45217</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>44974</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46090</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45237</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45958</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45959</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>46090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45816</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45036</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45964</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>45062</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>46094</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>46093</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45073</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45741</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>45049</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45551</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45342</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>46101</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>44623</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45978</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>45307</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45727</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45586</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44838</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>44838</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>46114</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45988</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>46119</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16417,7 +16417,7 @@
         <v>45988</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45994</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>45488</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45994</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>46126</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45994</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45148</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>46132</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>46132</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>44529</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44949</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45250</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45303</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46135</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45343</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>46139</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45462</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45350</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>44832</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45370</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>45600</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45891</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>45595</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44952</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>45601</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44979</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45180</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45749</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45593</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44489</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>44838</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>45274</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45775</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45645</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45798</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45727</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>44805</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>44922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>45726</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45675</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45642</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44952</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19561,7 +19561,7 @@
         <v>45775</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45867</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45623</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44882</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45097</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45257</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>45161</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>45870</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44903</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44489</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45259</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>45764</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45092</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45685</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45694</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45699</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45974</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45645</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45896</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45616</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45616</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>44811</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>44497</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>46163</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>44928</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>44928</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>44630</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44630</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>46170</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45033</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44627</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45622</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45014</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45870</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44645</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>46176</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>44630</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45226</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44823</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44823</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44956</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45219</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45629</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45103</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>44985</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44704</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45154</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45630</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>44957</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45161</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45606</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45384</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45187</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45225</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45226</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45084</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>46197</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45050</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>46202</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45194</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45609</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45169</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45203</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45511</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>46210</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45148</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45244</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>46210</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>46211</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>46043</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>46210</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>46211</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>46038</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45050</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>44812</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>46221</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>46221</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45236</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>46221</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45022</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46164</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>46264</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45197</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46269</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46269</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46269</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>44713</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>45705</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>45679</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>44952</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>46274</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45414</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45111</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>46274</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>46274</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
         <v>46276</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45107</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45112</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>45511</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45384</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>45085</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>45511</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44812</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>46287</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45511</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45553</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>46286</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>46288</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44690</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>45384</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>46288</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>46248</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>45352</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45539</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>46294</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28117,7 +28117,7 @@
         <v>46252</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>45210</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28263,7 +28263,7 @@
         <v>45271</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>45642</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45642</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45028</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>46252</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         <v>46252</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>46252</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>46252</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
         <v>45688</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>44722</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45700</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29066,7 +29066,7 @@
         <v>45700</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>46296</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>46296</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         <v>45217</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>46296</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>46296</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>45558</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45593</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44747</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45188</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>46296</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>46296</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29942,7 +29942,7 @@
         <v>46296</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>46254</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45559</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>45343</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45462</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45462</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>44592</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45204</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44987</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45076</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45426</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>45040</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45040</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>45485</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45168</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45622</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45646</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45777</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45777</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>45777</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45777</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45400</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>44980</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>44865</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>44981</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45355</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44981</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45716</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45939</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>46147</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>

--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>46230</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>45855</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>46034</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>44950</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45831</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45321</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>46139</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45264</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46251</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45366</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45072</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>45502</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45559</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45603</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44748</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45337</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45986</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45202</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45335</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45357</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45082</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45576</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>46006</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>46003</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>46055</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>46077</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45355</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44503</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44559</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44602</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44490</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44823</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44529</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44711</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44530</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44503</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>44707</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>44545</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44636</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44636</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>44497</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44529</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>44529</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44578</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44728</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44729</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44623</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44622</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45203</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44580</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44747</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45091</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45343</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>44824</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45705</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45485</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44747</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44922</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>45028</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45462</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45462</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>45363</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>45330</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44928</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45187</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45226</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45050</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44956</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45105</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45219</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45107</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45217</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45217</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>45188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45675</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45169</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45110</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45443</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44823</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>44823</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44952</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45226</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45226</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45426</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45062</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45595</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45257</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45187</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44489</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44957</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45352</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45462</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45540</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45204</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44811</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44630</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45324</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45123</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45646</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>44690</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45112</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45097</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45511</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45384</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45485</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>45384</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44980</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45488</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44985</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>45616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45093</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45775</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45622</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45050</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45049</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>45908</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45225</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45551</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45148</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45540</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45777</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45777</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45777</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45777</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>44987</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45076</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>45148</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45539</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45551</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>45343</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45022</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45606</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45586</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>44952</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45426</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>45350</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45728</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44489</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45559</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45925</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>45642</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45642</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>45014</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>45090</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>45073</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>45757</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45334</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>44838</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>44838</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>45740</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>45370</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>45740</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45233</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45278</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45925</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45168</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45930</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45709</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45618</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45525</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45511</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45511</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45757</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45550</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45180</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45649</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44630</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44630</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45623</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>45797</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45637</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45084</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45934</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45934</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45936</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44802</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45366</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45630</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45805</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44645</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45194</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44573</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>45511</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45103</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45473</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45808</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45808</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45679</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45940</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44974</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>45553</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45629</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45816</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45741</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45148</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45947</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>44623</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44713</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45694</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45727</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45609</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45154</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45685</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45085</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>44497</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>44949</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45700</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45414</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44529</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45958</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45959</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45454</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45303</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45199</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>45833</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45237</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45161</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45251</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45688</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45964</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44672</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45616</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45197</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45593</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45342</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45307</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45600</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45244</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45616</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45601</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>44952</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45250</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45593</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45727</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44704</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45726</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>44805</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45867</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45870</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45271</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>44812</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45687</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45210</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45622</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45259</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45236</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>46101</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44627</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45511</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>45700</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45700</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45988</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45988</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45111</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45162</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>46114</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45994</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>46119</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45994</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>45994</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44861</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>46126</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>45040</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45033</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45384</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>46132</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>46006</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45033</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>46003</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>46006</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44979</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>45161</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44812</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45645</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44592</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>46135</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45204</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45775</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45558</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>44594</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>44882</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>46010</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45642</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45891</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>45133</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>46029</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45798</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>46029</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45274</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44722</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>46038</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>46042</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>46042</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>46043</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45040</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>45755</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45146</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>45033</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>44838</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45749</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>46139</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>46045</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>44832</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>45111</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>45036</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>46055</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>46055</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>46057</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45728</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>46063</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>46069</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>46069</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>46071</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>46072</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46074</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45092</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45764</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45896</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>46090</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>45699</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>46090</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45645</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45974</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>46093</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>46094</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>46163</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45870</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>46170</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>46176</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>46197</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>46202</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>46210</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>46043</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>46210</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>46211</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>46210</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>46211</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>46038</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>46221</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>46221</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>46264</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>46164</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>46269</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>46274</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>46274</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>46274</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>46276</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>46286</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>46287</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>46288</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>46288</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>46288</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>46294</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>46248</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>46252</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>46252</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>46296</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>46296</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>46296</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>46252</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>46296</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46296</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46296</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>46296</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46252</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>46252</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>46254</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>46302</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46301</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>46304</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45400</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>44980</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44865</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>44981</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>45355</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44981</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45716</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45939</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>46147</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>

--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45847</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>46230</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>45855</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>46034</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>44950</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45831</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>45321</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>46139</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45264</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46251</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45366</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45072</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>45502</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45559</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45603</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44748</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45337</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45986</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>46003</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45202</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45335</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45635</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45357</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>45082</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45576</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>46006</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>46003</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>46055</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>46077</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45355</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44503</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44559</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44602</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44490</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44823</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44529</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44711</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44530</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44503</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>44707</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>44545</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44636</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44636</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>44497</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44529</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>44529</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44578</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44728</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44729</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44623</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44622</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45203</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44580</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44747</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45091</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45343</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>44824</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>45705</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45485</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44747</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44922</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>45028</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45462</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45462</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>45363</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>45330</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44928</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44928</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45187</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45226</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45050</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44956</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45105</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45219</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45107</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45217</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45217</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>45188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45675</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45169</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45110</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45443</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44823</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>44823</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44952</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45226</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45226</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45426</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45062</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45595</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45257</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45187</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44489</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44957</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45352</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45462</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45540</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45204</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44811</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44630</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45324</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45123</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45646</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>44690</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45112</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45097</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45511</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45384</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45485</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>45384</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44980</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45488</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44985</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>45616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45093</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45775</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45622</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45050</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45049</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>45908</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>45225</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45551</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45148</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45540</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45777</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45777</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45777</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45777</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>44987</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45076</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>45148</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45539</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45551</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>45343</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45022</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45606</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45586</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>44952</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45426</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>45350</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45728</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44489</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45559</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45925</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>45642</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45642</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>45014</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>45090</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>45073</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>45757</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45334</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>44838</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>44838</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>45740</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>45370</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>45740</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45233</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45278</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45925</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45168</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45930</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45709</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45618</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45525</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45511</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45511</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45757</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45550</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44629</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45180</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45649</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44630</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44630</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45623</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>45797</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45637</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45084</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45934</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45934</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45936</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44802</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45366</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>45630</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45805</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44645</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45194</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>44573</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>45511</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45103</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45473</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45808</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45808</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>45679</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>45940</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17704,7 +17704,7 @@
         <v>44974</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>45553</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45629</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>45816</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45741</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45148</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45947</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>44623</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>44713</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45694</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45727</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45609</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>45154</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45685</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45085</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>44497</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>44949</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45700</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45414</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>44529</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45958</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45959</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45454</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45303</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45199</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>45833</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45237</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45161</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45251</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45688</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45964</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44672</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45616</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>45197</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45593</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45342</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45307</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45600</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45244</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45616</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45601</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>44952</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45250</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45593</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45727</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44704</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45726</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>44805</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45867</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>45870</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>45271</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>44812</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45687</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45210</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45622</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45259</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45236</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>46101</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>44627</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>45511</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>45700</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45700</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45988</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45988</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45111</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45162</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>46114</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45994</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>46119</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45994</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>45994</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>44861</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>46126</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>45040</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23189,7 +23189,7 @@
         <v>45033</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45384</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>46132</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>46006</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45033</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>46003</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>46006</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44979</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>45161</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44812</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45645</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44592</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>46135</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>45204</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45775</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45558</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24362,7 +24362,7 @@
         <v>44594</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>44882</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>46010</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45642</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45891</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>45133</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>46029</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45798</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>46029</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45274</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44722</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>46038</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>46042</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>46042</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>46043</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45040</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>45755</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>45146</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>45033</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>44838</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45749</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>46139</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>46045</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>44832</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>45111</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>45036</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>46055</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>46055</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>46057</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45728</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>46063</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
         <v>46069</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>46069</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>46071</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>46072</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>46074</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>45092</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45764</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45896</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>46090</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>45699</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>46090</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45645</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45974</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>46093</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>46094</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>46163</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45870</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>46170</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>46176</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>46197</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>46202</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>46210</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>46043</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>46210</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         <v>46211</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>46210</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>46211</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28596,7 +28596,7 @@
         <v>46038</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28669,7 +28669,7 @@
         <v>46221</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>46221</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>46264</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         <v>46164</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>46269</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>46274</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>46274</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>46274</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>46276</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>46286</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>46287</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>46288</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>46288</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>46288</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>46294</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>46248</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>46252</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>46252</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>46296</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>46296</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>46296</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>46252</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>46296</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46296</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46296</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>46296</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>46252</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>46252</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>46254</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>46302</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>46301</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>46304</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45400</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>44980</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44865</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>44981</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>45355</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44981</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45716</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>45939</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>46147</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>

--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46230</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45847</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44950</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46034</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45855</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45321</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45264</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45551</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46251</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45502</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>45366</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45986</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>46003</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44748</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45072</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45603</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45337</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45335</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45202</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45082</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46003</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46006</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46055</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>46077</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45645</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45357</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45576</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45355</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44503</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44559</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44602</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44490</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44823</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44529</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44497</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44530</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44636</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44636</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44578</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>44729</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44711</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>44728</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44707</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44623</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44622</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44580</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44824</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45757</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45251</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45616</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45091</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>44802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45443</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45148</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45110</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>45105</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45755</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45123</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45187</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>45324</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45687</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>45085</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>45363</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>45334</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>45550</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45226</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45199</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>44861</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>44573</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45204</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44594</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44747</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45551</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45033</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44629</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45649</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45540</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45540</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45485</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45454</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45033</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45330</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>44672</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45217</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45237</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45036</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45062</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45073</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45049</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45307</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45551</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45342</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45586</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44838</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44838</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45891</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45749</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45488</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44630</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45775</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45645</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45148</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45798</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45642</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45250</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45343</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45908</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45462</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45909</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45350</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44832</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45370</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45595</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45925</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44979</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45180</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45925</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44489</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44838</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>45930</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45936</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>45934</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45274</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45934</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44805</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>44922</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45940</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45675</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>45764</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45947</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>44952</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45775</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45092</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45958</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45699</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>45959</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45974</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>45645</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>45623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>44882</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>45964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45257</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>45896</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>45161</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>44903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44489</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45978</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>46163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>45259</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>45685</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45694</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45988</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45616</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45616</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>44811</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45994</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45994</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44497</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45994</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>44928</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>44928</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>46170</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44630</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44630</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>46003</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45033</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44627</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>46006</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>46006</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45622</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45014</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>46010</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44645</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45870</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45226</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45133</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>44823</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44823</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44956</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>46029</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>46029</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45219</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45629</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45103</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>44985</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>46176</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>46038</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44704</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45154</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45630</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>46042</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>46042</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>46043</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>44957</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45161</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>46045</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45606</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45384</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45187</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45225</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>46055</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>46055</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45226</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>46057</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>45084</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45050</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>46063</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45728</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>46069</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45194</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>46069</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>46071</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>46072</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>46074</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45609</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45169</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45203</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45511</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46090</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45148</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45244</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>46090</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>46094</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>46093</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45050</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>46101</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44812</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>46197</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45236</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45022</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>46114</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>46119</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>46202</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>45197</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>46126</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>44713</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45705</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45679</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>44952</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>46132</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45414</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>45111</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>46135</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45107</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>46139</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45112</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45093</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45511</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45384</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45511</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44812</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>46210</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>46210</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>46211</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>46043</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>46210</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>46211</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46038</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45511</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>45553</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>46221</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46221</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>46164</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44690</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45384</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45352</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>46274</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>46274</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>46274</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>46276</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45539</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45271</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45642</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45642</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45028</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45688</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>44722</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45700</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45700</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45217</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45558</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45593</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>44747</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45188</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>46287</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45559</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45343</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>46286</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45462</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45462</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44592</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>46288</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45204</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46288</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>46288</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>46248</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>44987</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>45076</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>46294</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>46252</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45426</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45040</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45040</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45485</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45168</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>46252</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>46252</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>46252</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>46252</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45622</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>46296</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>46296</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46296</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46296</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>46296</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>46296</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>46296</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>46254</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45646</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45777</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45777</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45777</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45777</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>46301</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>46302</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45728</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45709</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45757</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45426</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45525</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45278</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45233</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45618</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45090</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>45740</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45740</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45797</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>46304</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>46264</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>45637</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>46307</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45366</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>45805</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45511</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>46309</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45808</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45808</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45473</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44974</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>46269</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45816</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45741</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44623</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45727</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>44529</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44949</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45833</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45303</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45600</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44952</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>45601</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45593</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45727</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45726</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45867</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45870</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45400</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44980</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44865</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44981</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45355</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44981</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45716</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45939</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>46147</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>

--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46230</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45847</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44950</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46034</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45855</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45321</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>45264</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45551</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>46251</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>45502</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>45366</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45986</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>46003</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45091</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>44748</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>45072</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45603</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45337</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45335</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>45635</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>45202</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>45082</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46003</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46006</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46055</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>46077</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45645</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>45357</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>45576</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45355</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44503</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44559</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44602</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44490</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44823</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>44503</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44529</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44497</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44530</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44545</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44636</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44636</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44578</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>44729</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44711</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44503</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>44728</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44707</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44623</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44622</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44580</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44824</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45757</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>45251</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45616</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>45091</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>44802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>45443</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45148</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45110</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>45105</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         <v>45755</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>45123</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45162</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45187</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>45324</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45687</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>45085</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>45363</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>45334</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>45550</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45226</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45199</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>44861</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>44573</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45204</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44594</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>44747</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45111</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45551</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45033</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44629</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45649</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45540</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45540</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45485</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45454</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45033</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45330</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>44672</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45217</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45237</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45036</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45062</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45073</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45049</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45307</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45551</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45342</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45586</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44838</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44838</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45146</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45891</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45749</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45488</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44630</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45775</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45645</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45148</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45798</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45642</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45250</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45343</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45908</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45462</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45909</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45350</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>44832</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45370</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45595</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45925</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44979</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45180</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45925</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44489</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44838</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>45930</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45936</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>45934</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45274</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45934</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>44805</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>44922</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45940</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45675</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>45764</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45947</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>44952</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45775</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45092</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45958</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45699</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>45959</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45974</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>45645</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>45623</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>44882</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>45964</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45097</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45257</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>45896</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>45161</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>44903</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44489</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45978</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>46163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>45259</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>45685</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45694</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45988</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45616</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45616</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>44811</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45994</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45994</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44497</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45994</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>44928</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>44928</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>46170</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>44630</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44630</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>46003</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45033</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44627</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>46006</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>46006</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>45622</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45014</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>46010</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>44645</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45870</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45226</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45133</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>44823</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44823</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44956</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>46029</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>46029</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45219</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45629</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45103</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>44985</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>46176</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>46038</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>44704</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45154</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45630</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>46042</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>46042</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>46043</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>44957</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45161</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>46045</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45606</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45384</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45187</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>45225</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>46055</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>46055</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45226</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>46057</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>45084</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>45050</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>46063</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45728</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>46069</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45194</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>46069</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>46071</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>46072</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>46074</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>45609</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45169</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45203</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45511</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46090</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45148</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45244</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>46090</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>46094</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>46093</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45050</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>46101</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>44812</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>46197</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45236</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45022</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>46114</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>46119</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>46202</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>45197</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>46126</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>44713</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45705</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45679</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>44952</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>46132</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45414</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>45111</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>46135</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45107</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>46139</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45112</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45093</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45511</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45384</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45511</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44812</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>46210</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>46210</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>46211</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>46043</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>46210</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>46211</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>46038</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45511</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>45553</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>46221</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46221</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>46164</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>44690</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45384</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45352</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>46274</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>46274</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>46274</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>46276</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>45539</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45271</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45642</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45642</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45028</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45688</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>44722</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24649,7 +24649,7 @@
         <v>45700</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>45700</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45217</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45558</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45593</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>44747</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45188</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>46287</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25233,7 +25233,7 @@
         <v>45559</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45343</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>46286</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45462</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45462</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44592</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>46288</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45204</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>46288</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>46288</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>46248</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>44987</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>45076</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>46294</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>46252</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45426</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45040</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45040</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45485</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45168</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>46252</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>46252</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>46252</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>46252</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26995,7 +26995,7 @@
         <v>45622</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>46296</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27141,7 +27141,7 @@
         <v>46296</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46296</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46296</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>46296</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>46296</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>46296</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>46254</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         <v>45646</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45777</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         <v>45777</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45777</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45777</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>46301</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>46302</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45728</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45709</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45757</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45426</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45525</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45278</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45233</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45618</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45090</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>45740</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>45740</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45797</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>46304</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>46264</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>45637</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>46307</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>45366</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>45805</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45511</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29550,7 +29550,7 @@
         <v>46309</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45808</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45808</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45473</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44974</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>46269</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>45816</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45741</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44623</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30207,7 +30207,7 @@
         <v>45727</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>44529</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44949</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45833</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45303</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45600</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>44952</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>45601</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45593</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45727</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45726</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45867</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45870</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45400</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44980</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44865</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44981</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45355</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44981</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45716</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45939</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>46147</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>

--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
         <v>22</v>
       </c>
       <c r="T3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46230</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45847</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44950</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46034</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45855</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45321</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>46251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45551</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45264</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45502</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45366</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>45072</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45986</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>46003</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45603</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45559</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45091</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45232</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45202</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>46006</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46003</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>45357</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>46077</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>45576</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45635</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45082</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>45645</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45335</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45355</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44503</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44559</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44602</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44823</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44739</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44503</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>44529</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44497</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44530</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44636</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44636</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44578</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44729</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>44711</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44503</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44728</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>44707</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44529</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44623</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44622</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45033</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44630</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44580</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44979</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44824</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45161</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44812</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45187</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45050</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45219</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44592</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>45204</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44594</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>44823</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44823</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44882</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45203</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45908</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45343</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45645</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45974</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45909</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>46163</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45274</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45705</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44722</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45925</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>45040</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45925</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45755</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45146</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45870</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>46170</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45033</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45934</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44838</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45934</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45936</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45363</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45111</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45036</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45940</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44747</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44928</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44928</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45226</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44747</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>46176</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45443</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44952</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45226</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45226</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45462</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45462</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>45426</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>45947</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45188</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45675</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45169</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>45110</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45959</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45964</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45062</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45187</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45257</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>46197</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45540</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45204</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45978</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>44811</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>46202</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45123</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45646</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>44690</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45097</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45988</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>45488</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>45616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>46210</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45093</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>46043</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>46210</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45775</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>46211</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>46210</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>46211</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>46038</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45994</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45994</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45994</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45462</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>45049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45225</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>46221</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>45777</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>46221</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>45777</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45777</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45777</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>46164</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>46006</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>46003</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>46006</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>46010</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45133</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45426</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45728</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45090</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>46029</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45757</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45740</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>46029</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45740</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45233</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45278</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>46286</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45709</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45618</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45525</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>46038</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>46042</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>46042</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>46287</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>46043</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45797</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45637</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>46288</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>46288</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>46045</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>46288</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45366</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>46055</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45805</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>46055</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45511</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>46057</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45473</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45808</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45808</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44974</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45728</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>46063</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>46294</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45816</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45741</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>44623</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>46248</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>46069</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>46069</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>45727</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45511</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>46071</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>46072</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>46074</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>46252</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>46252</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>46296</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>46296</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>46252</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>46296</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>46296</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>46296</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>46296</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>46252</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>46252</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>44949</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44529</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45303</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45833</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>46090</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>46090</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>46093</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45384</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45485</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>46094</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>46254</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46101</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45600</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45601</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44952</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>46302</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44985</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45593</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>46301</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45727</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45726</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46114</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>46304</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>46119</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45867</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45870</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>45622</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>46126</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>46264</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>46132</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45050</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45148</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45540</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45645</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>46135</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45775</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45551</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>46309</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45642</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45343</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45891</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45606</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>44952</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>46307</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45350</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45798</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>45559</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>46269</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45014</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44838</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44838</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45370</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>46315</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45511</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46315</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>46315</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45085</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>46315</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45550</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45749</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44629</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>46139</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>46276</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44630</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>44630</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>46274</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>46274</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>46274</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>45630</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>44645</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45553</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45092</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45764</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45896</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44713</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45699</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45694</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45609</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44497</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>45414</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45454</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45161</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45616</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45593</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45342</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45616</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45687</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45210</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>45622</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45236</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>45511</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45700</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45700</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45111</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45091</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45485</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>44922</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45028</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45330</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44956</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44903</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45105</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45107</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45217</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45217</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45595</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44957</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45352</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45324</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45112</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45384</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44980</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45551</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44987</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>45076</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45148</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45539</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45022</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45586</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>45642</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>45642</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>45073</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>45334</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>45168</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45511</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>45757</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>45180</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45649</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45623</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45084</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>44802</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45194</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44573</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45103</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>45679</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>45629</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45148</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45154</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45685</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45700</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45199</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45237</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>45251</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45688</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>44672</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>45197</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45307</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45244</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45250</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>44704</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44805</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45271</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44812</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45259</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44627</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45162</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44861</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45040</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45033</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45384</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45400</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44980</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44865</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44981</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45355</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44981</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45716</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45939</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>46147</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>

--- a/Översikt FALKÖPING.xlsx
+++ b/Översikt FALKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45946</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>44980</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45526</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>46230</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45847</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>45478</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44950</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>46034</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>45831</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>45855</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>46139</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>45321</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>45740</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>46251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45551</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45264</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>46246</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>45502</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>45366</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>45072</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45986</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>46003</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45603</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>45337</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45559</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>44748</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45091</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>45232</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46147</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45202</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>46006</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46003</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>45357</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>46055</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>46077</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>45576</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45635</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45082</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>45645</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>45335</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45355</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>44529</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44503</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>44559</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         <v>44602</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>44823</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44739</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>44503</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>44529</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44497</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44530</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44636</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44636</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44578</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44729</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>44711</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44503</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44728</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>44707</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44529</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>44529</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44623</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44622</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45033</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44630</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44580</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>44979</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44824</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>45161</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44812</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45187</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45050</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>45219</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44592</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>45204</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44594</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>44823</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44823</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44882</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45203</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45908</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45343</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45645</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>45974</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>45909</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>46163</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45274</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45705</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44722</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45925</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>45040</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45925</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45755</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45146</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45870</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>46170</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45033</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45934</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44838</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45934</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45936</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44832</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45363</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45111</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45036</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45940</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44747</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44928</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44928</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45226</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44747</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>46176</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45443</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44952</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45226</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45226</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>45462</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45462</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>45426</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>45947</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45188</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45675</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45169</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>45110</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45959</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45964</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45062</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45187</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45257</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>46197</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45540</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45204</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>45978</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>44811</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>46202</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45123</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45646</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>44690</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45097</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45988</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>45488</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45988</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>45616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>46210</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45093</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>46043</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>46210</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45775</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>46211</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>46210</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>46211</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>46038</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45994</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45994</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45994</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>45462</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>45049</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45225</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>46221</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14268,7 +14268,7 @@
         <v>45777</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14341,7 +14341,7 @@
         <v>46221</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>45777</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45777</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         <v>45777</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>46164</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>46006</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>46003</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>46006</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>46010</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45133</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45426</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45728</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45090</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>46029</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>45757</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45740</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>46029</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>45740</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45233</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45278</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>46286</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45709</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45618</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45525</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>46038</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>46042</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>46042</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>46287</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>46043</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45797</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45637</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>46288</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>46288</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>46045</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>46288</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45366</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>46055</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>45805</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>46055</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45511</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>46057</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45473</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45808</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>45808</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>44974</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>45728</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>46063</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>46294</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45816</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45741</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>44623</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>46248</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>46069</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>46069</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>45727</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45511</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>46071</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>46072</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>46074</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>46252</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>46252</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>46296</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>46296</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>46252</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>46296</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>46296</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>46296</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>46296</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>46252</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>46252</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>44949</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44529</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45303</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45833</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>46090</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>46090</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>46093</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45384</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45485</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>46094</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>46254</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20264,7 +20264,7 @@
         <v>46101</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45600</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45601</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44952</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>46302</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44985</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20702,7 +20702,7 @@
         <v>45593</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20775,7 +20775,7 @@
         <v>46301</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45727</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45726</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46114</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>46304</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>46119</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45867</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45870</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>45622</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21432,7 +21432,7 @@
         <v>46126</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>46264</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>46132</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45050</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45148</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45540</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45645</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>46135</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45775</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45551</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>46309</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22235,7 +22235,7 @@
         <v>45642</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>45343</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45891</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         <v>45606</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>44952</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>46307</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45350</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>45798</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>45559</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>46269</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22965,7 +22965,7 @@
         <v>45014</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         <v>44838</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44838</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45370</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         <v>46315</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45511</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>46315</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>46315</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45085</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>46315</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>45550</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>45749</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>44629</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>46139</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>46276</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44630</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>44630</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>46274</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>46274</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>46274</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>45630</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>44645</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45553</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45092</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45764</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45896</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>44713</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45699</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>45694</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>45609</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44497</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>45414</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45454</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>45161</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45616</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45593</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>45342</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>45616</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45687</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>45210</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>45622</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45236</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>45511</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>45700</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45700</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45111</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45091</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45485</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>44922</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45028</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26620,7 +26620,7 @@
         <v>45330</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>44956</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44903</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>45105</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45107</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45217</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45217</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45595</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27204,7 +27204,7 @@
         <v>44957</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45352</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45324</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45112</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45384</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44980</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45551</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44987</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27788,7 +27788,7 @@
         <v>45076</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27861,7 +27861,7 @@
         <v>45148</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45539</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>45022</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45586</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>45642</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>45642</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>45073</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>45334</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>45168</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45511</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28591,7 +28591,7 @@
         <v>45757</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>45180</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45649</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         <v>45623</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45084</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>44802</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45194</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>44573</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45103</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29253,7 +29253,7 @@
         <v>45679</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>45629</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45148</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45154</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45685</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45700</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45199</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45237</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>45251</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29910,7 +29910,7 @@
         <v>45688</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>44672</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>45197</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45307</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45244</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45250</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>44704</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44805</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>45271</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>44812</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45259</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44627</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45162</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>44861</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45040</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45033</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>45384</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45400</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>44980</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44865</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>44981</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>45355</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>44981</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45716</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>45939</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>46147</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
